--- a/data/extracted/inventory-receipts/CONTENEDOR DUBAI SOFT 25 MARZO.xlsx
+++ b/data/extracted/inventory-receipts/CONTENEDOR DUBAI SOFT 25 MARZO.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3647BEE9-D0E5-495B-AD99-F5CA685E8F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -3728,7 +3730,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -3769,12 +3771,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4054,50 +4055,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L952"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -4135,12 +4136,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -4178,7 +4179,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -4216,7 +4217,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -4254,7 +4255,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4292,7 +4293,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4330,7 +4331,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -4368,7 +4369,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4406,7 +4407,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -4444,7 +4445,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -4482,7 +4483,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -4520,7 +4521,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -4558,7 +4559,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -4596,7 +4597,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -4634,7 +4635,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -4672,7 +4673,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -4710,7 +4711,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -4748,7 +4749,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -4786,7 +4787,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -4824,7 +4825,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -4862,7 +4863,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -4900,7 +4901,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -4938,7 +4939,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -4976,7 +4977,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -5014,7 +5015,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -5052,7 +5053,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -5090,7 +5091,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -5128,7 +5129,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -5166,7 +5167,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -5204,7 +5205,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -5242,7 +5243,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -5280,7 +5281,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -5318,7 +5319,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -5356,7 +5357,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -5394,7 +5395,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -5432,7 +5433,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -5470,7 +5471,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -5508,7 +5509,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -5546,7 +5547,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -5584,7 +5585,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -5622,7 +5623,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -5660,7 +5661,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -5736,7 +5737,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -5774,7 +5775,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -5812,7 +5813,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -5850,7 +5851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -5888,7 +5889,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -5926,7 +5927,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -6002,7 +6003,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -6040,7 +6041,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -6078,7 +6079,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -6116,7 +6117,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -6154,7 +6155,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -6192,7 +6193,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -6230,7 +6231,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -6268,7 +6269,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -6306,7 +6307,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6344,7 +6345,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -6420,7 +6421,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -6458,7 +6459,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -6496,7 +6497,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -6534,7 +6535,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -6572,7 +6573,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -6610,7 +6611,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -6648,7 +6649,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -6686,7 +6687,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -6724,7 +6725,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -6762,7 +6763,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -6800,7 +6801,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -6838,7 +6839,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -6876,7 +6877,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -6914,7 +6915,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -6952,7 +6953,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -6990,7 +6991,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -7028,7 +7029,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -7066,7 +7067,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F84" s="1" t="s">
         <v>179</v>
       </c>
@@ -7086,7 +7087,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F85" s="1" t="s">
         <v>181</v>
       </c>
@@ -7106,7 +7107,7 @@
         <v>1822.3</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -7144,7 +7145,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -7182,7 +7183,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -7220,7 +7221,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -7258,7 +7259,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -7296,7 +7297,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -7334,7 +7335,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -7372,7 +7373,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -7410,7 +7411,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -7448,7 +7449,7 @@
         <v>30.4</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -7486,7 +7487,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -7524,7 +7525,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -7562,7 +7563,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -7600,7 +7601,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -7638,7 +7639,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -7676,7 +7677,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -7714,7 +7715,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -7752,7 +7753,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -7790,7 +7791,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -7828,7 +7829,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -7866,7 +7867,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -7904,7 +7905,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -7942,7 +7943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -7980,7 +7981,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -8018,7 +8019,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8056,7 +8057,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -8094,7 +8095,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -8132,7 +8133,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -8170,7 +8171,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -8208,7 +8209,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -8246,7 +8247,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -8284,7 +8285,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -8322,7 +8323,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -8360,7 +8361,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -8398,7 +8399,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -8436,7 +8437,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -8474,7 +8475,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -8512,7 +8513,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -8550,7 +8551,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -8588,7 +8589,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -8664,7 +8665,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -8702,7 +8703,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -8740,7 +8741,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -8778,7 +8779,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -8816,7 +8817,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -8854,7 +8855,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -8892,7 +8893,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -8930,7 +8931,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -8968,7 +8969,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -9006,7 +9007,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -9044,7 +9045,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -9082,7 +9083,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -9120,7 +9121,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -9158,7 +9159,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -9196,7 +9197,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -9234,7 +9235,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -9310,7 +9311,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -9348,7 +9349,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -9386,7 +9387,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -9424,7 +9425,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -9462,7 +9463,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -9500,7 +9501,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -9538,7 +9539,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -9576,7 +9577,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -9614,7 +9615,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -9652,7 +9653,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -9690,7 +9691,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -9728,7 +9729,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -9766,7 +9767,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -9804,7 +9805,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -9842,7 +9843,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -9880,7 +9881,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -9918,7 +9919,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -9956,7 +9957,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -9994,7 +9995,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -10032,7 +10033,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -10070,7 +10071,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -10108,7 +10109,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -10146,7 +10147,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -10184,7 +10185,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -10222,7 +10223,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -10260,7 +10261,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -10298,7 +10299,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -10336,7 +10337,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -10374,7 +10375,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -10412,7 +10413,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -10450,7 +10451,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -10488,7 +10489,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -10526,7 +10527,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -10564,7 +10565,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -10602,7 +10603,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -10640,7 +10641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -10678,7 +10679,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -10716,7 +10717,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -10754,7 +10755,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -10792,7 +10793,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -10868,7 +10869,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -10906,7 +10907,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -10944,7 +10945,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -10982,7 +10983,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -11020,7 +11021,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -11058,7 +11059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -11096,7 +11097,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -11134,7 +11135,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -11172,7 +11173,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -11210,7 +11211,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -11248,7 +11249,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -11286,7 +11287,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -11324,7 +11325,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -11362,7 +11363,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -11400,7 +11401,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -11438,7 +11439,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -11476,7 +11477,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -11514,7 +11515,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -11552,7 +11553,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -11590,7 +11591,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -11628,7 +11629,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -11666,7 +11667,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -11704,7 +11705,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -11742,7 +11743,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -11780,7 +11781,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F209" s="1" t="s">
         <v>179</v>
       </c>
@@ -11800,7 +11801,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F210" s="1" t="s">
         <v>354</v>
       </c>
@@ -11820,7 +11821,7 @@
         <v>2875.4</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -11858,7 +11859,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -11896,7 +11897,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -11934,7 +11935,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -11972,7 +11973,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -12010,7 +12011,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -12048,7 +12049,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -12086,7 +12087,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -12124,7 +12125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -12162,7 +12163,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -12200,7 +12201,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -12238,7 +12239,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -12276,7 +12277,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -12314,7 +12315,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -12352,7 +12353,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -12390,7 +12391,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -12428,7 +12429,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -12466,7 +12467,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -12504,7 +12505,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -12542,7 +12543,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -12580,7 +12581,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -12618,7 +12619,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -12656,7 +12657,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F233" s="1" t="s">
         <v>179</v>
       </c>
@@ -12676,7 +12677,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F234" s="1" t="s">
         <v>380</v>
       </c>
@@ -12696,7 +12697,7 @@
         <v>501.4</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -12734,7 +12735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -12772,7 +12773,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -12810,7 +12811,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -12848,7 +12849,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -12886,7 +12887,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -12924,7 +12925,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -12962,7 +12963,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -13000,7 +13001,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -13038,7 +13039,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -13076,7 +13077,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -13114,7 +13115,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -13152,7 +13153,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -13190,7 +13191,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -13228,7 +13229,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -13266,7 +13267,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -13304,7 +13305,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -13342,7 +13343,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -13380,7 +13381,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -13418,7 +13419,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -13456,7 +13457,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -13494,7 +13495,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -13532,7 +13533,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F257" s="1" t="s">
         <v>179</v>
       </c>
@@ -13552,7 +13553,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F258" s="1" t="s">
         <v>380</v>
       </c>
@@ -13572,7 +13573,7 @@
         <v>526.4</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>19</v>
       </c>
@@ -13610,7 +13611,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>19</v>
       </c>
@@ -13648,7 +13649,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -13686,7 +13687,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -13724,7 +13725,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -13762,7 +13763,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -13800,7 +13801,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -13838,7 +13839,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -13876,7 +13877,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -13914,7 +13915,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -13952,7 +13953,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -13990,7 +13991,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -14028,7 +14029,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -14066,7 +14067,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -14104,7 +14105,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -14142,7 +14143,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -14180,7 +14181,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -14218,7 +14219,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -14256,7 +14257,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -14294,7 +14295,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -14332,7 +14333,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -14370,7 +14371,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -14408,7 +14409,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -14446,7 +14447,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -14484,7 +14485,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -14522,7 +14523,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -14560,7 +14561,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -14598,7 +14599,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -14636,7 +14637,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -14674,7 +14675,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -14712,7 +14713,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -14750,7 +14751,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -14788,7 +14789,7 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -14826,7 +14827,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -14864,7 +14865,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -14902,7 +14903,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -14940,7 +14941,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>19</v>
       </c>
@@ -14978,7 +14979,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -15016,7 +15017,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -15054,7 +15055,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -15092,7 +15093,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -15130,7 +15131,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -15168,7 +15169,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -15206,7 +15207,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -15244,7 +15245,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -15282,7 +15283,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -15320,7 +15321,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -15358,7 +15359,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -15396,7 +15397,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -15434,7 +15435,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -15472,7 +15473,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -15510,7 +15511,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>19</v>
       </c>
@@ -15548,7 +15549,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -15586,7 +15587,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -15624,7 +15625,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -15662,7 +15663,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -15700,7 +15701,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>19</v>
       </c>
@@ -15738,7 +15739,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -15776,7 +15777,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -15814,7 +15815,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -15852,7 +15853,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>19</v>
       </c>
@@ -15890,7 +15891,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>19</v>
       </c>
@@ -15928,7 +15929,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -15966,7 +15967,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -16004,7 +16005,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -16042,7 +16043,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -16080,7 +16081,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -16118,7 +16119,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -16156,7 +16157,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -16194,7 +16195,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -16232,7 +16233,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -16270,7 +16271,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -16308,7 +16309,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -16346,7 +16347,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -16384,7 +16385,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -16422,7 +16423,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -16460,7 +16461,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -16498,7 +16499,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -16536,7 +16537,7 @@
         <v>26.9</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -16574,7 +16575,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -16612,7 +16613,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>19</v>
       </c>
@@ -16650,7 +16651,7 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -16688,7 +16689,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -16726,7 +16727,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -16764,7 +16765,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -16802,7 +16803,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>19</v>
       </c>
@@ -16840,7 +16841,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -16878,7 +16879,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -16916,7 +16917,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -16954,7 +16955,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -16992,7 +16993,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -17030,7 +17031,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
@@ -17068,7 +17069,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>19</v>
       </c>
@@ -17106,7 +17107,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -17144,7 +17145,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -17182,7 +17183,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -17220,7 +17221,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -17258,7 +17259,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -17296,7 +17297,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -17334,7 +17335,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -17372,7 +17373,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -17410,7 +17411,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -17448,7 +17449,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -17486,7 +17487,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -17524,7 +17525,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -17562,7 +17563,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -17600,7 +17601,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -17638,7 +17639,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -17676,7 +17677,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -17714,7 +17715,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -17752,7 +17753,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>19</v>
       </c>
@@ -17790,7 +17791,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>19</v>
       </c>
@@ -17828,7 +17829,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>19</v>
       </c>
@@ -17866,7 +17867,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>19</v>
       </c>
@@ -17904,7 +17905,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -17942,7 +17943,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -17980,7 +17981,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>19</v>
       </c>
@@ -18018,7 +18019,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>19</v>
       </c>
@@ -18056,7 +18057,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>19</v>
       </c>
@@ -18094,7 +18095,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>19</v>
       </c>
@@ -18132,7 +18133,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>19</v>
       </c>
@@ -18170,7 +18171,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F380" s="1" t="s">
         <v>179</v>
       </c>
@@ -18190,7 +18191,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F381" s="1" t="s">
         <v>530</v>
       </c>
@@ -18210,7 +18211,7 @@
         <v>2846.1</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>19</v>
       </c>
@@ -18248,7 +18249,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>19</v>
       </c>
@@ -18286,7 +18287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>19</v>
       </c>
@@ -18324,7 +18325,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -18362,7 +18363,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>19</v>
       </c>
@@ -18400,7 +18401,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -18438,7 +18439,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>19</v>
       </c>
@@ -18476,7 +18477,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>19</v>
       </c>
@@ -18514,7 +18515,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>19</v>
       </c>
@@ -18552,7 +18553,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>19</v>
       </c>
@@ -18590,7 +18591,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>19</v>
       </c>
@@ -18628,7 +18629,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>19</v>
       </c>
@@ -18666,7 +18667,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>19</v>
       </c>
@@ -18704,7 +18705,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -18742,7 +18743,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>19</v>
       </c>
@@ -18780,7 +18781,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>19</v>
       </c>
@@ -18818,7 +18819,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>19</v>
       </c>
@@ -18856,7 +18857,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>19</v>
       </c>
@@ -18894,7 +18895,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -18932,7 +18933,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>19</v>
       </c>
@@ -18970,7 +18971,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>19</v>
       </c>
@@ -19008,7 +19009,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>19</v>
       </c>
@@ -19046,7 +19047,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>19</v>
       </c>
@@ -19084,7 +19085,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>19</v>
       </c>
@@ -19122,7 +19123,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>19</v>
       </c>
@@ -19160,7 +19161,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>19</v>
       </c>
@@ -19198,7 +19199,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>19</v>
       </c>
@@ -19236,7 +19237,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>19</v>
       </c>
@@ -19274,7 +19275,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>19</v>
       </c>
@@ -19312,7 +19313,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>19</v>
       </c>
@@ -19350,7 +19351,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>19</v>
       </c>
@@ -19388,7 +19389,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -19426,7 +19427,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>19</v>
       </c>
@@ -19464,7 +19465,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>19</v>
       </c>
@@ -19502,7 +19503,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>19</v>
       </c>
@@ -19540,7 +19541,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>19</v>
       </c>
@@ -19578,7 +19579,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -19616,7 +19617,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>19</v>
       </c>
@@ -19654,7 +19655,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>19</v>
       </c>
@@ -19692,7 +19693,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>19</v>
       </c>
@@ -19730,7 +19731,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -19768,7 +19769,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>19</v>
       </c>
@@ -19806,7 +19807,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -19844,7 +19845,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>19</v>
       </c>
@@ -19882,7 +19883,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>19</v>
       </c>
@@ -19920,7 +19921,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>19</v>
       </c>
@@ -19958,7 +19959,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>19</v>
       </c>
@@ -19996,7 +19997,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -20034,7 +20035,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>19</v>
       </c>
@@ -20072,7 +20073,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>19</v>
       </c>
@@ -20110,7 +20111,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -20148,7 +20149,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>19</v>
       </c>
@@ -20186,7 +20187,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>19</v>
       </c>
@@ -20224,7 +20225,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -20262,7 +20263,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>19</v>
       </c>
@@ -20300,7 +20301,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>19</v>
       </c>
@@ -20338,7 +20339,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>19</v>
       </c>
@@ -20376,7 +20377,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>19</v>
       </c>
@@ -20414,7 +20415,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>19</v>
       </c>
@@ -20452,7 +20453,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>19</v>
       </c>
@@ -20490,7 +20491,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>19</v>
       </c>
@@ -20528,7 +20529,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>19</v>
       </c>
@@ -20566,7 +20567,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>19</v>
       </c>
@@ -20604,7 +20605,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>19</v>
       </c>
@@ -20642,7 +20643,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>19</v>
       </c>
@@ -20680,7 +20681,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>19</v>
       </c>
@@ -20718,7 +20719,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>19</v>
       </c>
@@ -20756,7 +20757,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -20794,7 +20795,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>19</v>
       </c>
@@ -20832,7 +20833,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>19</v>
       </c>
@@ -20870,7 +20871,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>19</v>
       </c>
@@ -20908,7 +20909,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -20946,7 +20947,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>19</v>
       </c>
@@ -20984,7 +20985,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>19</v>
       </c>
@@ -21022,7 +21023,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -21060,7 +21061,7 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>19</v>
       </c>
@@ -21098,7 +21099,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>19</v>
       </c>
@@ -21136,7 +21137,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>19</v>
       </c>
@@ -21174,7 +21175,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -21212,7 +21213,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>19</v>
       </c>
@@ -21250,7 +21251,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>19</v>
       </c>
@@ -21288,7 +21289,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>19</v>
       </c>
@@ -21326,7 +21327,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -21364,7 +21365,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>19</v>
       </c>
@@ -21402,7 +21403,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>19</v>
       </c>
@@ -21440,7 +21441,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -21478,7 +21479,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>19</v>
       </c>
@@ -21516,7 +21517,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>19</v>
       </c>
@@ -21554,7 +21555,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -21592,7 +21593,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>19</v>
       </c>
@@ -21630,7 +21631,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -21668,7 +21669,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>19</v>
       </c>
@@ -21706,7 +21707,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>19</v>
       </c>
@@ -21744,7 +21745,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>19</v>
       </c>
@@ -21782,7 +21783,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>19</v>
       </c>
@@ -21820,7 +21821,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>19</v>
       </c>
@@ -21858,7 +21859,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -21896,7 +21897,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>19</v>
       </c>
@@ -21934,7 +21935,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>19</v>
       </c>
@@ -21972,7 +21973,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>19</v>
       </c>
@@ -22010,7 +22011,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -22048,7 +22049,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>19</v>
       </c>
@@ -22086,7 +22087,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -22124,7 +22125,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>19</v>
       </c>
@@ -22162,7 +22163,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>19</v>
       </c>
@@ -22200,7 +22201,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -22238,7 +22239,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>19</v>
       </c>
@@ -22276,7 +22277,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>19</v>
       </c>
@@ -22314,7 +22315,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>19</v>
       </c>
@@ -22352,7 +22353,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>19</v>
       </c>
@@ -22390,7 +22391,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -22428,7 +22429,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>19</v>
       </c>
@@ -22466,7 +22467,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>19</v>
       </c>
@@ -22504,7 +22505,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>19</v>
       </c>
@@ -22542,7 +22543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -22580,7 +22581,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>19</v>
       </c>
@@ -22618,7 +22619,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>19</v>
       </c>
@@ -22656,7 +22657,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>19</v>
       </c>
@@ -22694,7 +22695,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -22732,7 +22733,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>19</v>
       </c>
@@ -22770,7 +22771,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>19</v>
       </c>
@@ -22808,7 +22809,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F503" s="1" t="s">
         <v>179</v>
       </c>
@@ -22828,7 +22829,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F504" s="1" t="s">
         <v>530</v>
       </c>
@@ -22848,7 +22849,7 @@
         <v>2823.4</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>19</v>
       </c>
@@ -22886,7 +22887,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -22924,7 +22925,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>19</v>
       </c>
@@ -22962,7 +22963,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>19</v>
       </c>
@@ -23000,7 +23001,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -23038,7 +23039,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>19</v>
       </c>
@@ -23076,7 +23077,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>19</v>
       </c>
@@ -23114,7 +23115,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>19</v>
       </c>
@@ -23152,7 +23153,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>19</v>
       </c>
@@ -23190,7 +23191,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -23228,7 +23229,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>19</v>
       </c>
@@ -23266,7 +23267,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>19</v>
       </c>
@@ -23304,7 +23305,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>19</v>
       </c>
@@ -23342,7 +23343,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>19</v>
       </c>
@@ -23380,7 +23381,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -23418,7 +23419,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>19</v>
       </c>
@@ -23456,7 +23457,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>19</v>
       </c>
@@ -23494,7 +23495,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>19</v>
       </c>
@@ -23532,7 +23533,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>19</v>
       </c>
@@ -23570,7 +23571,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>19</v>
       </c>
@@ -23608,7 +23609,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>19</v>
       </c>
@@ -23646,7 +23647,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>19</v>
       </c>
@@ -23684,7 +23685,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>19</v>
       </c>
@@ -23722,7 +23723,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -23760,7 +23761,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>19</v>
       </c>
@@ -23798,7 +23799,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>19</v>
       </c>
@@ -23836,7 +23837,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>19</v>
       </c>
@@ -23874,7 +23875,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -23912,7 +23913,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>19</v>
       </c>
@@ -23950,7 +23951,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>19</v>
       </c>
@@ -23988,7 +23989,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>19</v>
       </c>
@@ -24026,7 +24027,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>19</v>
       </c>
@@ -24064,7 +24065,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>19</v>
       </c>
@@ -24102,7 +24103,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>19</v>
       </c>
@@ -24140,7 +24141,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>19</v>
       </c>
@@ -24178,7 +24179,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -24216,7 +24217,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>19</v>
       </c>
@@ -24254,7 +24255,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>19</v>
       </c>
@@ -24292,7 +24293,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>19</v>
       </c>
@@ -24330,7 +24331,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>19</v>
       </c>
@@ -24368,7 +24369,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -24406,7 +24407,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>19</v>
       </c>
@@ -24444,7 +24445,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>19</v>
       </c>
@@ -24482,7 +24483,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>19</v>
       </c>
@@ -24520,7 +24521,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -24558,7 +24559,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>19</v>
       </c>
@@ -24596,7 +24597,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>19</v>
       </c>
@@ -24634,7 +24635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -24672,7 +24673,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>19</v>
       </c>
@@ -24710,7 +24711,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -24748,7 +24749,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>19</v>
       </c>
@@ -24786,7 +24787,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>19</v>
       </c>
@@ -24824,7 +24825,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -24862,7 +24863,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>19</v>
       </c>
@@ -24900,7 +24901,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>19</v>
       </c>
@@ -24938,7 +24939,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>19</v>
       </c>
@@ -24976,7 +24977,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>19</v>
       </c>
@@ -25014,7 +25015,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -25052,7 +25053,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>19</v>
       </c>
@@ -25090,7 +25091,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>19</v>
       </c>
@@ -25128,7 +25129,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>19</v>
       </c>
@@ -25166,7 +25167,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -25204,7 +25205,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>19</v>
       </c>
@@ -25242,7 +25243,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>19</v>
       </c>
@@ -25280,7 +25281,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>19</v>
       </c>
@@ -25318,7 +25319,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>19</v>
       </c>
@@ -25356,7 +25357,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>19</v>
       </c>
@@ -25394,7 +25395,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
         <v>19</v>
       </c>
@@ -25432,7 +25433,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -25470,7 +25471,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>19</v>
       </c>
@@ -25508,7 +25509,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>19</v>
       </c>
@@ -25546,7 +25547,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>19</v>
       </c>
@@ -25584,7 +25585,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>19</v>
       </c>
@@ -25622,7 +25623,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>19</v>
       </c>
@@ -25660,7 +25661,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -25698,7 +25699,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>19</v>
       </c>
@@ -25736,7 +25737,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>19</v>
       </c>
@@ -25774,7 +25775,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -25812,7 +25813,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>19</v>
       </c>
@@ -25850,7 +25851,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>19</v>
       </c>
@@ -25888,7 +25889,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>19</v>
       </c>
@@ -25926,7 +25927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>19</v>
       </c>
@@ -25964,7 +25965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -26002,7 +26003,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>19</v>
       </c>
@@ -26040,7 +26041,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>19</v>
       </c>
@@ -26078,7 +26079,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>19</v>
       </c>
@@ -26116,7 +26117,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -26154,7 +26155,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>19</v>
       </c>
@@ -26192,7 +26193,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>19</v>
       </c>
@@ -26230,7 +26231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -26268,7 +26269,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>19</v>
       </c>
@@ -26306,7 +26307,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>19</v>
       </c>
@@ -26344,7 +26345,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>19</v>
       </c>
@@ -26382,7 +26383,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>19</v>
       </c>
@@ -26420,7 +26421,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>19</v>
       </c>
@@ -26458,7 +26459,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>19</v>
       </c>
@@ -26496,7 +26497,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>19</v>
       </c>
@@ -26534,7 +26535,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>19</v>
       </c>
@@ -26572,7 +26573,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>19</v>
       </c>
@@ -26610,7 +26611,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>19</v>
       </c>
@@ -26648,7 +26649,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>19</v>
       </c>
@@ -26686,7 +26687,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>19</v>
       </c>
@@ -26724,7 +26725,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="s">
         <v>19</v>
       </c>
@@ -26762,7 +26763,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>19</v>
       </c>
@@ -26800,7 +26801,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="s">
         <v>19</v>
       </c>
@@ -26838,7 +26839,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>19</v>
       </c>
@@ -26876,7 +26877,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>19</v>
       </c>
@@ -26914,7 +26915,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>19</v>
       </c>
@@ -26952,7 +26953,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>19</v>
       </c>
@@ -26990,7 +26991,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>19</v>
       </c>
@@ -27028,7 +27029,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="s">
         <v>19</v>
       </c>
@@ -27066,7 +27067,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
         <v>19</v>
       </c>
@@ -27104,7 +27105,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>19</v>
       </c>
@@ -27142,7 +27143,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>19</v>
       </c>
@@ -27180,7 +27181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>19</v>
       </c>
@@ -27218,7 +27219,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>19</v>
       </c>
@@ -27256,7 +27257,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="s">
         <v>19</v>
       </c>
@@ -27294,7 +27295,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
         <v>19</v>
       </c>
@@ -27332,7 +27333,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>19</v>
       </c>
@@ -27370,7 +27371,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>19</v>
       </c>
@@ -27408,7 +27409,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>19</v>
       </c>
@@ -27446,7 +27447,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
         <v>19</v>
       </c>
@@ -27484,7 +27485,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="s">
         <v>19</v>
       </c>
@@ -27522,7 +27523,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
         <v>19</v>
       </c>
@@ -27560,7 +27561,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>19</v>
       </c>
@@ -27598,7 +27599,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
         <v>19</v>
       </c>
@@ -27636,7 +27637,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="s">
         <v>19</v>
       </c>
@@ -27674,7 +27675,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>19</v>
       </c>
@@ -27712,7 +27713,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="s">
         <v>19</v>
       </c>
@@ -27750,7 +27751,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>19</v>
       </c>
@@ -27788,7 +27789,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>19</v>
       </c>
@@ -27826,7 +27827,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>19</v>
       </c>
@@ -27864,7 +27865,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
         <v>19</v>
       </c>
@@ -27902,7 +27903,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
         <v>19</v>
       </c>
@@ -27940,7 +27941,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>19</v>
       </c>
@@ -27978,7 +27979,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
         <v>19</v>
       </c>
@@ -28016,7 +28017,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>19</v>
       </c>
@@ -28054,7 +28055,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
         <v>19</v>
       </c>
@@ -28092,7 +28093,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>19</v>
       </c>
@@ -28130,7 +28131,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>19</v>
       </c>
@@ -28168,7 +28169,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>19</v>
       </c>
@@ -28206,7 +28207,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>19</v>
       </c>
@@ -28244,7 +28245,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="s">
         <v>19</v>
       </c>
@@ -28282,7 +28283,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
         <v>19</v>
       </c>
@@ -28320,7 +28321,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="s">
         <v>19</v>
       </c>
@@ -28358,7 +28359,7 @@
         <v>18.8</v>
       </c>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>19</v>
       </c>
@@ -28396,7 +28397,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="s">
         <v>19</v>
       </c>
@@ -28434,7 +28435,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>19</v>
       </c>
@@ -28472,7 +28473,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="s">
         <v>19</v>
       </c>
@@ -28510,7 +28511,7 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
         <v>19</v>
       </c>
@@ -28548,7 +28549,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>19</v>
       </c>
@@ -28586,7 +28587,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
         <v>19</v>
       </c>
@@ -28624,7 +28625,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="s">
         <v>19</v>
       </c>
@@ -28662,7 +28663,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
         <v>19</v>
       </c>
@@ -28700,7 +28701,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="s">
         <v>19</v>
       </c>
@@ -28738,7 +28739,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
         <v>19</v>
       </c>
@@ -28776,7 +28777,7 @@
         <v>22.8</v>
       </c>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="s">
         <v>19</v>
       </c>
@@ -28814,7 +28815,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
         <v>19</v>
       </c>
@@ -28852,7 +28853,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="s">
         <v>19</v>
       </c>
@@ -28890,7 +28891,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>19</v>
       </c>
@@ -28928,7 +28929,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="s">
         <v>19</v>
       </c>
@@ -28966,7 +28967,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>19</v>
       </c>
@@ -29004,7 +29005,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>19</v>
       </c>
@@ -29042,7 +29043,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
         <v>19</v>
       </c>
@@ -29080,7 +29081,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>19</v>
       </c>
@@ -29118,7 +29119,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>19</v>
       </c>
@@ -29156,7 +29157,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>19</v>
       </c>
@@ -29194,7 +29195,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
         <v>19</v>
       </c>
@@ -29232,7 +29233,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>19</v>
       </c>
@@ -29270,7 +29271,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>19</v>
       </c>
@@ -29308,7 +29309,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>19</v>
       </c>
@@ -29346,7 +29347,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>19</v>
       </c>
@@ -29384,7 +29385,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="s">
         <v>19</v>
       </c>
@@ -29422,7 +29423,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
         <v>19</v>
       </c>
@@ -29460,7 +29461,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>19</v>
       </c>
@@ -29498,7 +29499,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>19</v>
       </c>
@@ -29536,7 +29537,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="s">
         <v>19</v>
       </c>
@@ -29574,7 +29575,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="s">
         <v>19</v>
       </c>
@@ -29612,7 +29613,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>19</v>
       </c>
@@ -29650,7 +29651,7 @@
         <v>25.2</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>19</v>
       </c>
@@ -29688,7 +29689,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="s">
         <v>19</v>
       </c>
@@ -29726,7 +29727,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>19</v>
       </c>
@@ -29764,7 +29765,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="s">
         <v>19</v>
       </c>
@@ -29802,7 +29803,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="s">
         <v>19</v>
       </c>
@@ -29840,7 +29841,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="s">
         <v>19</v>
       </c>
@@ -29878,7 +29879,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="s">
         <v>19</v>
       </c>
@@ -29916,7 +29917,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="s">
         <v>19</v>
       </c>
@@ -29954,7 +29955,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>19</v>
       </c>
@@ -29992,7 +29993,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="s">
         <v>19</v>
       </c>
@@ -30030,7 +30031,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="s">
         <v>19</v>
       </c>
@@ -30068,7 +30069,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="s">
         <v>19</v>
       </c>
@@ -30106,7 +30107,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>19</v>
       </c>
@@ -30144,7 +30145,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="s">
         <v>19</v>
       </c>
@@ -30182,7 +30183,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="s">
         <v>19</v>
       </c>
@@ -30220,7 +30221,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="1" t="s">
         <v>19</v>
       </c>
@@ -30258,7 +30259,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="1" t="s">
         <v>19</v>
       </c>
@@ -30296,7 +30297,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>19</v>
       </c>
@@ -30334,7 +30335,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="1" t="s">
         <v>19</v>
       </c>
@@ -30372,7 +30373,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="1" t="s">
         <v>19</v>
       </c>
@@ -30410,7 +30411,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="1" t="s">
         <v>19</v>
       </c>
@@ -30448,7 +30449,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>19</v>
       </c>
@@ -30486,7 +30487,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>19</v>
       </c>
@@ -30524,7 +30525,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>19</v>
       </c>
@@ -30562,7 +30563,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="1" t="s">
         <v>19</v>
       </c>
@@ -30600,7 +30601,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>19</v>
       </c>
@@ -30638,7 +30639,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="1" t="s">
         <v>19</v>
       </c>
@@ -30676,7 +30677,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>19</v>
       </c>
@@ -30714,7 +30715,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="712" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="1" t="s">
         <v>19</v>
       </c>
@@ -30752,7 +30753,7 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>19</v>
       </c>
@@ -30790,7 +30791,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>19</v>
       </c>
@@ -30828,7 +30829,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="1" t="s">
         <v>19</v>
       </c>
@@ -30866,7 +30867,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="1" t="s">
         <v>19</v>
       </c>
@@ -30904,7 +30905,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="717" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="1" t="s">
         <v>19</v>
       </c>
@@ -30942,7 +30943,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>19</v>
       </c>
@@ -30980,7 +30981,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="719" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="1" t="s">
         <v>19</v>
       </c>
@@ -31018,7 +31019,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>19</v>
       </c>
@@ -31056,7 +31057,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="721" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="1" t="s">
         <v>19</v>
       </c>
@@ -31094,7 +31095,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>19</v>
       </c>
@@ -31132,7 +31133,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>19</v>
       </c>
@@ -31170,7 +31171,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>19</v>
       </c>
@@ -31208,7 +31209,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="725" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A725" s="1" t="s">
         <v>19</v>
       </c>
@@ -31246,7 +31247,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>19</v>
       </c>
@@ -31284,7 +31285,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="727" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A727" s="1" t="s">
         <v>19</v>
       </c>
@@ -31322,7 +31323,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>19</v>
       </c>
@@ -31360,7 +31361,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="729" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A729" s="1" t="s">
         <v>19</v>
       </c>
@@ -31398,7 +31399,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>19</v>
       </c>
@@ -31436,7 +31437,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>19</v>
       </c>
@@ -31474,7 +31475,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>19</v>
       </c>
@@ -31512,7 +31513,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="733" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A733" s="1" t="s">
         <v>19</v>
       </c>
@@ -31550,7 +31551,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="734" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A734" s="1" t="s">
         <v>19</v>
       </c>
@@ -31588,7 +31589,7 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>19</v>
       </c>
@@ -31626,7 +31627,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>19</v>
       </c>
@@ -31664,7 +31665,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="737" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A737" s="1" t="s">
         <v>19</v>
       </c>
@@ -31702,7 +31703,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="738" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A738" s="1" t="s">
         <v>19</v>
       </c>
@@ -31740,7 +31741,7 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>19</v>
       </c>
@@ -31778,7 +31779,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>19</v>
       </c>
@@ -31816,7 +31817,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>19</v>
       </c>
@@ -31854,7 +31855,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="742" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A742" s="1" t="s">
         <v>19</v>
       </c>
@@ -31892,7 +31893,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="743" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A743" s="1" t="s">
         <v>19</v>
       </c>
@@ -31930,7 +31931,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>19</v>
       </c>
@@ -31968,7 +31969,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>19</v>
       </c>
@@ -32006,7 +32007,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>19</v>
       </c>
@@ -32044,7 +32045,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="747" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A747" s="1" t="s">
         <v>19</v>
       </c>
@@ -32082,7 +32083,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>19</v>
       </c>
@@ -32120,7 +32121,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="749" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A749" s="1" t="s">
         <v>19</v>
       </c>
@@ -32158,7 +32159,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="750" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A750" s="1" t="s">
         <v>19</v>
       </c>
@@ -32196,7 +32197,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="1" t="s">
         <v>19</v>
       </c>
@@ -32234,7 +32235,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="752" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A752" s="1" t="s">
         <v>19</v>
       </c>
@@ -32272,7 +32273,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="753" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A753" s="1" t="s">
         <v>19</v>
       </c>
@@ -32310,7 +32311,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="754" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A754" s="1" t="s">
         <v>19</v>
       </c>
@@ -32348,7 +32349,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="755" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A755" s="1" t="s">
         <v>19</v>
       </c>
@@ -32386,7 +32387,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="756" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A756" s="1" t="s">
         <v>19</v>
       </c>
@@ -32424,7 +32425,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="757" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A757" s="1" t="s">
         <v>19</v>
       </c>
@@ -32462,7 +32463,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="758" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A758" s="1" t="s">
         <v>19</v>
       </c>
@@ -32500,7 +32501,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="759" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A759" s="1" t="s">
         <v>19</v>
       </c>
@@ -32538,7 +32539,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="760" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A760" s="1" t="s">
         <v>19</v>
       </c>
@@ -32576,7 +32577,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="761" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A761" s="1" t="s">
         <v>19</v>
       </c>
@@ -32614,7 +32615,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="762" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A762" s="1" t="s">
         <v>19</v>
       </c>
@@ -32652,7 +32653,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="763" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A763" s="1" t="s">
         <v>19</v>
       </c>
@@ -32690,7 +32691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="764" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A764" s="1" t="s">
         <v>19</v>
       </c>
@@ -32728,7 +32729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="765" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A765" s="1" t="s">
         <v>19</v>
       </c>
@@ -32766,7 +32767,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="766" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A766" s="1" t="s">
         <v>19</v>
       </c>
@@ -32804,7 +32805,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="767" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A767" s="1" t="s">
         <v>19</v>
       </c>
@@ -32842,7 +32843,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="768" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A768" s="1" t="s">
         <v>19</v>
       </c>
@@ -32880,7 +32881,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="769" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A769" s="1" t="s">
         <v>19</v>
       </c>
@@ -32918,7 +32919,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="770" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A770" s="1" t="s">
         <v>19</v>
       </c>
@@ -32956,7 +32957,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="771" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F771" s="1" t="s">
         <v>179</v>
       </c>
@@ -32976,7 +32977,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="772" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F772" s="1" t="s">
         <v>1067</v>
       </c>
@@ -32996,7 +32997,7 @@
         <v>6488.1</v>
       </c>
     </row>
-    <row r="773" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A773" s="1" t="s">
         <v>19</v>
       </c>
@@ -33034,7 +33035,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="774" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A774" s="1" t="s">
         <v>19</v>
       </c>
@@ -33072,7 +33073,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="775" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
         <v>19</v>
       </c>
@@ -33110,7 +33111,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="776" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A776" s="1" t="s">
         <v>19</v>
       </c>
@@ -33148,7 +33149,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="777" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A777" s="1" t="s">
         <v>19</v>
       </c>
@@ -33186,7 +33187,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="778" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A778" s="1" t="s">
         <v>19</v>
       </c>
@@ -33224,7 +33225,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="779" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A779" s="1" t="s">
         <v>19</v>
       </c>
@@ -33262,7 +33263,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="780" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A780" s="1" t="s">
         <v>19</v>
       </c>
@@ -33300,7 +33301,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="781" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A781" s="1" t="s">
         <v>19</v>
       </c>
@@ -33338,7 +33339,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="782" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A782" s="1" t="s">
         <v>19</v>
       </c>
@@ -33376,7 +33377,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="783" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A783" s="1" t="s">
         <v>19</v>
       </c>
@@ -33414,7 +33415,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="784" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A784" s="1" t="s">
         <v>19</v>
       </c>
@@ -33452,7 +33453,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="785" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A785" s="1" t="s">
         <v>19</v>
       </c>
@@ -33490,7 +33491,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="786" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A786" s="1" t="s">
         <v>19</v>
       </c>
@@ -33528,7 +33529,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="787" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A787" s="1" t="s">
         <v>19</v>
       </c>
@@ -33566,7 +33567,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="788" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A788" s="1" t="s">
         <v>19</v>
       </c>
@@ -33604,7 +33605,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="789" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A789" s="1" t="s">
         <v>19</v>
       </c>
@@ -33642,7 +33643,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="790" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A790" s="1" t="s">
         <v>19</v>
       </c>
@@ -33680,7 +33681,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="791" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A791" s="1" t="s">
         <v>19</v>
       </c>
@@ -33718,7 +33719,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="792" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A792" s="1" t="s">
         <v>19</v>
       </c>
@@ -33756,7 +33757,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="793" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A793" s="1" t="s">
         <v>19</v>
       </c>
@@ -33794,7 +33795,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="794" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A794" s="1" t="s">
         <v>19</v>
       </c>
@@ -33832,7 +33833,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="795" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F795" s="1" t="s">
         <v>179</v>
       </c>
@@ -33852,7 +33853,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="796" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F796" s="1" t="s">
         <v>380</v>
       </c>
@@ -33872,7 +33873,7 @@
         <v>514.9</v>
       </c>
     </row>
-    <row r="797" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A797" s="1" t="s">
         <v>19</v>
       </c>
@@ -33910,7 +33911,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="798" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A798" s="1" t="s">
         <v>19</v>
       </c>
@@ -33948,7 +33949,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="799" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A799" s="1" t="s">
         <v>19</v>
       </c>
@@ -33986,7 +33987,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="800" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A800" s="1" t="s">
         <v>19</v>
       </c>
@@ -34024,7 +34025,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="801" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A801" s="1" t="s">
         <v>19</v>
       </c>
@@ -34062,7 +34063,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="802" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A802" s="1" t="s">
         <v>19</v>
       </c>
@@ -34100,7 +34101,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="803" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A803" s="1" t="s">
         <v>19</v>
       </c>
@@ -34138,7 +34139,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="804" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A804" s="1" t="s">
         <v>19</v>
       </c>
@@ -34176,7 +34177,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="805" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A805" s="1" t="s">
         <v>19</v>
       </c>
@@ -34214,7 +34215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="806" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A806" s="1" t="s">
         <v>19</v>
       </c>
@@ -34252,7 +34253,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="807" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A807" s="1" t="s">
         <v>19</v>
       </c>
@@ -34290,7 +34291,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="808" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A808" s="1" t="s">
         <v>19</v>
       </c>
@@ -34328,7 +34329,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="809" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A809" s="1" t="s">
         <v>19</v>
       </c>
@@ -34366,7 +34367,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="810" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A810" s="1" t="s">
         <v>19</v>
       </c>
@@ -34404,7 +34405,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="811" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A811" s="1" t="s">
         <v>19</v>
       </c>
@@ -34442,7 +34443,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="812" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A812" s="1" t="s">
         <v>19</v>
       </c>
@@ -34480,7 +34481,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="813" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A813" s="1" t="s">
         <v>19</v>
       </c>
@@ -34518,7 +34519,7 @@
         <v>29.4</v>
       </c>
     </row>
-    <row r="814" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A814" s="1" t="s">
         <v>19</v>
       </c>
@@ -34556,7 +34557,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="815" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A815" s="1" t="s">
         <v>19</v>
       </c>
@@ -34594,7 +34595,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="816" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A816" s="1" t="s">
         <v>19</v>
       </c>
@@ -34632,7 +34633,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="817" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A817" s="1" t="s">
         <v>19</v>
       </c>
@@ -34670,7 +34671,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="818" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A818" s="1" t="s">
         <v>19</v>
       </c>
@@ -34708,7 +34709,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="819" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A819" s="1" t="s">
         <v>19</v>
       </c>
@@ -34746,7 +34747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="820" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A820" s="1" t="s">
         <v>19</v>
       </c>
@@ -34784,7 +34785,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="821" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A821" s="1" t="s">
         <v>19</v>
       </c>
@@ -34822,7 +34823,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="822" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A822" s="1" t="s">
         <v>19</v>
       </c>
@@ -34860,7 +34861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="823" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A823" s="1" t="s">
         <v>19</v>
       </c>
@@ -34898,7 +34899,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="824" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A824" s="1" t="s">
         <v>19</v>
       </c>
@@ -34936,7 +34937,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="825" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A825" s="1" t="s">
         <v>19</v>
       </c>
@@ -34974,7 +34975,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="826" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A826" s="1" t="s">
         <v>19</v>
       </c>
@@ -35012,7 +35013,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="827" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A827" s="1" t="s">
         <v>19</v>
       </c>
@@ -35050,7 +35051,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="828" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A828" s="1" t="s">
         <v>19</v>
       </c>
@@ -35088,7 +35089,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="829" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A829" s="1" t="s">
         <v>19</v>
       </c>
@@ -35126,7 +35127,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="830" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A830" s="1" t="s">
         <v>19</v>
       </c>
@@ -35164,7 +35165,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="831" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A831" s="1" t="s">
         <v>19</v>
       </c>
@@ -35202,7 +35203,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="832" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A832" s="1" t="s">
         <v>19</v>
       </c>
@@ -35240,7 +35241,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="833" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A833" s="1" t="s">
         <v>19</v>
       </c>
@@ -35278,7 +35279,7 @@
         <v>22.2</v>
       </c>
     </row>
-    <row r="834" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A834" s="1" t="s">
         <v>19</v>
       </c>
@@ -35316,7 +35317,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="835" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A835" s="1" t="s">
         <v>19</v>
       </c>
@@ -35354,7 +35355,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="836" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A836" s="1" t="s">
         <v>19</v>
       </c>
@@ -35392,7 +35393,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="837" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A837" s="1" t="s">
         <v>19</v>
       </c>
@@ -35430,7 +35431,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="838" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A838" s="1" t="s">
         <v>19</v>
       </c>
@@ -35468,7 +35469,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="839" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A839" s="1" t="s">
         <v>19</v>
       </c>
@@ -35506,7 +35507,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="840" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A840" s="1" t="s">
         <v>19</v>
       </c>
@@ -35544,7 +35545,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="841" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F841" s="1" t="s">
         <v>179</v>
       </c>
@@ -35564,7 +35565,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="842" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F842" s="1" t="s">
         <v>1140</v>
       </c>
@@ -35584,7 +35585,7 @@
         <v>1053.4000000000001</v>
       </c>
     </row>
-    <row r="843" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A843" s="1" t="s">
         <v>19</v>
       </c>
@@ -35622,7 +35623,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="844" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A844" s="1" t="s">
         <v>19</v>
       </c>
@@ -35660,7 +35661,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="845" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A845" s="1" t="s">
         <v>19</v>
       </c>
@@ -35698,7 +35699,7 @@
         <v>29.3</v>
       </c>
     </row>
-    <row r="846" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A846" s="1" t="s">
         <v>19</v>
       </c>
@@ -35736,7 +35737,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="847" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A847" s="1" t="s">
         <v>19</v>
       </c>
@@ -35774,7 +35775,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="848" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A848" s="1" t="s">
         <v>19</v>
       </c>
@@ -35812,7 +35813,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="849" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A849" s="1" t="s">
         <v>19</v>
       </c>
@@ -35850,7 +35851,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="850" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A850" s="1" t="s">
         <v>19</v>
       </c>
@@ -35888,7 +35889,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="851" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A851" s="1" t="s">
         <v>19</v>
       </c>
@@ -35926,7 +35927,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="852" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A852" s="1" t="s">
         <v>19</v>
       </c>
@@ -35964,7 +35965,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="853" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A853" s="1" t="s">
         <v>19</v>
       </c>
@@ -36002,7 +36003,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="854" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A854" s="1" t="s">
         <v>19</v>
       </c>
@@ -36040,7 +36041,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="855" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A855" s="1" t="s">
         <v>19</v>
       </c>
@@ -36078,7 +36079,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="856" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A856" s="1" t="s">
         <v>19</v>
       </c>
@@ -36116,7 +36117,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="857" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A857" s="1" t="s">
         <v>19</v>
       </c>
@@ -36154,7 +36155,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="858" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A858" s="1" t="s">
         <v>19</v>
       </c>
@@ -36192,7 +36193,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="859" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A859" s="1" t="s">
         <v>19</v>
       </c>
@@ -36230,7 +36231,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="860" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A860" s="1" t="s">
         <v>19</v>
       </c>
@@ -36268,7 +36269,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="861" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A861" s="1" t="s">
         <v>19</v>
       </c>
@@ -36306,7 +36307,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="862" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A862" s="1" t="s">
         <v>19</v>
       </c>
@@ -36344,7 +36345,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="863" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A863" s="1" t="s">
         <v>19</v>
       </c>
@@ -36382,7 +36383,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="864" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A864" s="1" t="s">
         <v>19</v>
       </c>
@@ -36420,7 +36421,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="865" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F865" s="1" t="s">
         <v>179</v>
       </c>
@@ -36440,7 +36441,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="866" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F866" s="1" t="s">
         <v>380</v>
       </c>
@@ -36460,7 +36461,7 @@
         <v>535.1</v>
       </c>
     </row>
-    <row r="867" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A867" s="1" t="s">
         <v>19</v>
       </c>
@@ -36498,7 +36499,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="868" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A868" s="1" t="s">
         <v>19</v>
       </c>
@@ -36536,7 +36537,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="869" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A869" s="1" t="s">
         <v>19</v>
       </c>
@@ -36574,7 +36575,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="870" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A870" s="1" t="s">
         <v>19</v>
       </c>
@@ -36612,7 +36613,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="871" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A871" s="1" t="s">
         <v>19</v>
       </c>
@@ -36650,7 +36651,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="872" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A872" s="1" t="s">
         <v>19</v>
       </c>
@@ -36688,7 +36689,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="873" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A873" s="1" t="s">
         <v>19</v>
       </c>
@@ -36726,7 +36727,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="874" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A874" s="1" t="s">
         <v>19</v>
       </c>
@@ -36764,7 +36765,7 @@
         <v>23.4</v>
       </c>
     </row>
-    <row r="875" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A875" s="1" t="s">
         <v>19</v>
       </c>
@@ -36802,7 +36803,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="876" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A876" s="1" t="s">
         <v>19</v>
       </c>
@@ -36840,7 +36841,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="877" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A877" s="1" t="s">
         <v>19</v>
       </c>
@@ -36878,7 +36879,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="878" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A878" s="1" t="s">
         <v>19</v>
       </c>
@@ -36916,7 +36917,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="879" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A879" s="1" t="s">
         <v>19</v>
       </c>
@@ -36954,7 +36955,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="880" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A880" s="1" t="s">
         <v>19</v>
       </c>
@@ -36992,7 +36993,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="881" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A881" s="1" t="s">
         <v>19</v>
       </c>
@@ -37030,7 +37031,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="882" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A882" s="1" t="s">
         <v>19</v>
       </c>
@@ -37068,7 +37069,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="883" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A883" s="1" t="s">
         <v>19</v>
       </c>
@@ -37106,7 +37107,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="884" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A884" s="1" t="s">
         <v>19</v>
       </c>
@@ -37144,7 +37145,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="885" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A885" s="1" t="s">
         <v>19</v>
       </c>
@@ -37182,7 +37183,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="886" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A886" s="1" t="s">
         <v>19</v>
       </c>
@@ -37220,7 +37221,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="887" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A887" s="1" t="s">
         <v>19</v>
       </c>
@@ -37258,7 +37259,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="888" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
         <v>19</v>
       </c>
@@ -37296,7 +37297,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="889" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A889" s="1" t="s">
         <v>19</v>
       </c>
@@ -37334,7 +37335,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="890" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A890" s="1" t="s">
         <v>19</v>
       </c>
@@ -37372,7 +37373,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="891" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A891" s="1" t="s">
         <v>19</v>
       </c>
@@ -37410,7 +37411,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="892" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A892" s="1" t="s">
         <v>19</v>
       </c>
@@ -37448,7 +37449,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="893" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A893" s="1" t="s">
         <v>19</v>
       </c>
@@ -37486,7 +37487,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="894" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A894" s="1" t="s">
         <v>19</v>
       </c>
@@ -37524,7 +37525,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="895" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A895" s="1" t="s">
         <v>19</v>
       </c>
@@ -37562,7 +37563,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="896" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A896" s="1" t="s">
         <v>19</v>
       </c>
@@ -37600,7 +37601,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="897" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A897" s="1" t="s">
         <v>19</v>
       </c>
@@ -37638,7 +37639,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="898" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A898" s="1" t="s">
         <v>19</v>
       </c>
@@ -37676,7 +37677,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="899" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A899" s="1" t="s">
         <v>19</v>
       </c>
@@ -37714,7 +37715,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="900" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A900" s="1" t="s">
         <v>19</v>
       </c>
@@ -37752,7 +37753,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="901" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A901" s="1" t="s">
         <v>19</v>
       </c>
@@ -37790,7 +37791,7 @@
         <v>23.6</v>
       </c>
     </row>
-    <row r="902" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A902" s="1" t="s">
         <v>19</v>
       </c>
@@ -37828,7 +37829,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="903" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A903" s="1" t="s">
         <v>19</v>
       </c>
@@ -37866,7 +37867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="904" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A904" s="1" t="s">
         <v>19</v>
       </c>
@@ -37904,7 +37905,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="905" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A905" s="1" t="s">
         <v>19</v>
       </c>
@@ -37942,7 +37943,7 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="906" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A906" s="1" t="s">
         <v>19</v>
       </c>
@@ -37980,7 +37981,7 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="907" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A907" s="1" t="s">
         <v>19</v>
       </c>
@@ -38018,7 +38019,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="908" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A908" s="1" t="s">
         <v>19</v>
       </c>
@@ -38056,7 +38057,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="909" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A909" s="1" t="s">
         <v>19</v>
       </c>
@@ -38094,7 +38095,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="910" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A910" s="1" t="s">
         <v>19</v>
       </c>
@@ -38132,7 +38133,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="911" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F911" s="1" t="s">
         <v>179</v>
       </c>
@@ -38152,7 +38153,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="912" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F912" s="1" t="s">
         <v>1140</v>
       </c>
@@ -38172,7 +38173,7 @@
         <v>1060.3</v>
       </c>
     </row>
-    <row r="913" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F913" s="1" t="s">
         <v>179</v>
       </c>
@@ -38192,7 +38193,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="914" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F914" s="1" t="s">
         <v>1213</v>
       </c>
@@ -38212,7 +38213,7 @@
         <v>21046.799999999999</v>
       </c>
     </row>
-    <row r="915" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A915" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38250,7 +38251,7 @@
         <v>103.3</v>
       </c>
     </row>
-    <row r="916" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F916" s="1" t="s">
         <v>179</v>
       </c>
@@ -38270,7 +38271,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="917" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F917" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38290,7 +38291,7 @@
         <v>103.3</v>
       </c>
     </row>
-    <row r="918" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A918" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38328,7 +38329,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="919" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F919" s="1" t="s">
         <v>179</v>
       </c>
@@ -38348,7 +38349,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="920" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F920" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38368,7 +38369,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="921" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A921" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38406,7 +38407,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="922" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F922" s="1" t="s">
         <v>179</v>
       </c>
@@ -38426,7 +38427,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="923" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F923" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38446,7 +38447,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="924" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A924" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38484,7 +38485,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="925" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F925" s="1" t="s">
         <v>179</v>
       </c>
@@ -38504,7 +38505,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="926" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F926" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38524,7 +38525,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="927" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A927" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38562,7 +38563,7 @@
         <v>156.4</v>
       </c>
     </row>
-    <row r="928" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F928" s="1" t="s">
         <v>179</v>
       </c>
@@ -38582,7 +38583,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="929" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F929" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38602,7 +38603,7 @@
         <v>156.4</v>
       </c>
     </row>
-    <row r="930" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A930" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38640,7 +38641,7 @@
         <v>183.4</v>
       </c>
     </row>
-    <row r="931" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F931" s="1" t="s">
         <v>179</v>
       </c>
@@ -38660,7 +38661,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="932" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F932" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38680,7 +38681,7 @@
         <v>183.4</v>
       </c>
     </row>
-    <row r="933" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A933" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38718,7 +38719,7 @@
         <v>366.3</v>
       </c>
     </row>
-    <row r="934" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F934" s="1" t="s">
         <v>179</v>
       </c>
@@ -38738,7 +38739,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="935" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F935" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38758,7 +38759,7 @@
         <v>366.3</v>
       </c>
     </row>
-    <row r="936" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A936" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38796,7 +38797,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="937" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F937" s="1" t="s">
         <v>179</v>
       </c>
@@ -38816,7 +38817,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="938" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F938" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38836,7 +38837,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="939" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A939" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38874,7 +38875,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="940" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F940" s="1" t="s">
         <v>179</v>
       </c>
@@ -38894,7 +38895,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="941" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F941" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38914,7 +38915,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="942" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A942" s="1" t="s">
         <v>1214</v>
       </c>
@@ -38952,7 +38953,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="943" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F943" s="1" t="s">
         <v>179</v>
       </c>
@@ -38972,7 +38973,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="944" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F944" s="1" t="s">
         <v>1218</v>
       </c>
@@ -38992,7 +38993,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="945" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A945" s="1" t="s">
         <v>1214</v>
       </c>
@@ -39030,7 +39031,7 @@
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="946" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F946" s="1" t="s">
         <v>179</v>
       </c>
@@ -39050,7 +39051,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="947" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F947" s="1" t="s">
         <v>1218</v>
       </c>
@@ -39070,7 +39071,7 @@
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="948" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F948" s="1" t="s">
         <v>179</v>
       </c>
@@ -39090,7 +39091,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="949" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F949" s="1" t="s">
         <v>1229</v>
       </c>
@@ -39110,7 +39111,7 @@
         <v>1235.0999999999999</v>
       </c>
     </row>
-    <row r="950" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F950" s="1" t="s">
         <v>179</v>
       </c>
@@ -39130,7 +39131,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="951" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F951" s="1" t="s">
         <v>1230</v>
       </c>
@@ -39150,7 +39151,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="952" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F952" s="1" t="s">
         <v>179</v>
       </c>
@@ -39174,4 +39175,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4B7DC05-C876-4C9C-B014-B083A78460CA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47528</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>